--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileEstimatedBillImportError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileEstimatedBillImportError.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>业务单号</t>
   </si>
@@ -106,6 +106,27 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>币种</t>
+    </r>
+  </si>
+  <si>
     <t>错误信息</t>
   </si>
   <si>
@@ -125,6 +146,9 @@
   </si>
   <si>
     <t>{.costValue}</t>
+  </si>
+  <si>
+    <t>{.currency}</t>
   </si>
   <si>
     <t>{.errorMsg}</t>
@@ -140,7 +164,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,6 +328,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1108,8 +1138,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
@@ -1117,10 +1147,11 @@
     <col min="4" max="4" width="14.75" customWidth="1"/>
     <col min="5" max="5" width="13.125" customWidth="1"/>
     <col min="6" max="6" width="12.375" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="7" max="7" width="11.125" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1" spans="1:7">
+    <row r="1" ht="16" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1139,31 +1170,37 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileEstimatedBillImportError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileEstimatedBillImportError.xlsx
@@ -29,37 +29,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>来源单号</t>
+  </si>
+  <si>
+    <t>物流运单号</t>
+  </si>
   <si>
     <t>业务单号</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>物流运单号</t>
-    </r>
-  </si>
-  <si>
-    <t>来源单号</t>
-  </si>
-  <si>
-    <t>物流跟踪号</t>
   </si>
   <si>
     <r>
@@ -130,16 +108,13 @@
     <t>错误信息</t>
   </si>
   <si>
+    <t>{.sourceCode}</t>
+  </si>
+  <si>
+    <t>{.transportNo}</t>
+  </si>
+  <si>
     <t>{.businessCode}</t>
-  </si>
-  <si>
-    <t>{.transportNo}</t>
-  </si>
-  <si>
-    <t>{.sourceCode}</t>
-  </si>
-  <si>
-    <t>{.trackNo}</t>
   </si>
   <si>
     <t>{.costName}</t>
@@ -1138,30 +1113,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.25" customWidth="1"/>
+    <col min="1" max="1" width="14.625" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="3" width="14.625" customWidth="1"/>
-    <col min="4" max="4" width="14.75" customWidth="1"/>
-    <col min="5" max="5" width="13.125" customWidth="1"/>
-    <col min="6" max="6" width="12.375" customWidth="1"/>
-    <col min="7" max="7" width="11.125" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="3" max="3" width="14.25" customWidth="1"/>
+    <col min="4" max="4" width="13.125" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="11.125" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1" spans="1:8">
+    <row r="1" ht="16" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -1170,37 +1144,31 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
